--- a/artfynd/A 41767-2026 artfynd.xlsx
+++ b/artfynd/A 41767-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137309277</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137309279</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137309281</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137309276</v>
       </c>
       <c r="B5" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137309280</v>
       </c>
       <c r="B6" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137309302</v>
       </c>
       <c r="B7" t="n">
-        <v>96882</v>
+        <v>96883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137309307</v>
       </c>
       <c r="B8" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>137309253</v>
       </c>
       <c r="B21" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>137309254</v>
       </c>
       <c r="B22" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>137309256</v>
       </c>
       <c r="B23" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>137309257</v>
       </c>
       <c r="B24" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>137309258</v>
       </c>
       <c r="B25" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>137309259</v>
       </c>
       <c r="B26" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>137309265</v>
       </c>
       <c r="B27" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>137309267</v>
       </c>
       <c r="B28" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>137309269</v>
       </c>
       <c r="B29" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>137309278</v>
       </c>
       <c r="B30" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>137309283</v>
       </c>
       <c r="B31" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>137309288</v>
       </c>
       <c r="B32" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>137309293</v>
       </c>
       <c r="B33" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>137309296</v>
       </c>
       <c r="B34" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>137309303</v>
       </c>
       <c r="B35" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 41767-2026 artfynd.xlsx
+++ b/artfynd/A 41767-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137309277</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137309279</v>
       </c>
       <c r="B3" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137309281</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137309276</v>
       </c>
       <c r="B5" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137309280</v>
       </c>
       <c r="B6" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137309302</v>
       </c>
       <c r="B7" t="n">
-        <v>96883</v>
+        <v>96888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137309307</v>
       </c>
       <c r="B8" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137309262</v>
       </c>
       <c r="B9" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137309284</v>
       </c>
       <c r="B10" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>137309253</v>
       </c>
       <c r="B21" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>137309254</v>
       </c>
       <c r="B22" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>137309256</v>
       </c>
       <c r="B23" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>137309257</v>
       </c>
       <c r="B24" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>137309258</v>
       </c>
       <c r="B25" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>137309259</v>
       </c>
       <c r="B26" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>137309265</v>
       </c>
       <c r="B27" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>137309267</v>
       </c>
       <c r="B28" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>137309269</v>
       </c>
       <c r="B29" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>137309278</v>
       </c>
       <c r="B30" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>137309283</v>
       </c>
       <c r="B31" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>137309288</v>
       </c>
       <c r="B32" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>137309293</v>
       </c>
       <c r="B33" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>137309296</v>
       </c>
       <c r="B34" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>137309303</v>
       </c>
       <c r="B35" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 41767-2026 artfynd.xlsx
+++ b/artfynd/A 41767-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137309277</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137309279</v>
       </c>
       <c r="B3" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137309281</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137309276</v>
       </c>
       <c r="B5" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137309280</v>
       </c>
       <c r="B6" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137309302</v>
       </c>
       <c r="B7" t="n">
-        <v>96888</v>
+        <v>96890</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137309307</v>
       </c>
       <c r="B8" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>137309253</v>
       </c>
       <c r="B21" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>137309254</v>
       </c>
       <c r="B22" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>137309256</v>
       </c>
       <c r="B23" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>137309257</v>
       </c>
       <c r="B24" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>137309258</v>
       </c>
       <c r="B25" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>137309259</v>
       </c>
       <c r="B26" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>137309265</v>
       </c>
       <c r="B27" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>137309267</v>
       </c>
       <c r="B28" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>137309269</v>
       </c>
       <c r="B29" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>137309278</v>
       </c>
       <c r="B30" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>137309283</v>
       </c>
       <c r="B31" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>137309288</v>
       </c>
       <c r="B32" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>137309293</v>
       </c>
       <c r="B33" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>137309296</v>
       </c>
       <c r="B34" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>137309303</v>
       </c>
       <c r="B35" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 41767-2026 artfynd.xlsx
+++ b/artfynd/A 41767-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137309277</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137309279</v>
       </c>
       <c r="B3" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137309281</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137309276</v>
       </c>
       <c r="B5" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137309280</v>
       </c>
       <c r="B6" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137309302</v>
       </c>
       <c r="B7" t="n">
-        <v>96890</v>
+        <v>96896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137309307</v>
       </c>
       <c r="B8" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137309262</v>
       </c>
       <c r="B9" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137309284</v>
       </c>
       <c r="B10" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>137309253</v>
       </c>
       <c r="B21" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>137309254</v>
       </c>
       <c r="B22" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>137309256</v>
       </c>
       <c r="B23" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>137309257</v>
       </c>
       <c r="B24" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>137309258</v>
       </c>
       <c r="B25" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>137309259</v>
       </c>
       <c r="B26" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>137309265</v>
       </c>
       <c r="B27" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>137309267</v>
       </c>
       <c r="B28" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>137309269</v>
       </c>
       <c r="B29" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>137309278</v>
       </c>
       <c r="B30" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>137309283</v>
       </c>
       <c r="B31" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>137309288</v>
       </c>
       <c r="B32" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>137309293</v>
       </c>
       <c r="B33" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>137309296</v>
       </c>
       <c r="B34" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>137309303</v>
       </c>
       <c r="B35" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 41767-2026 artfynd.xlsx
+++ b/artfynd/A 41767-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137309277</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137309279</v>
       </c>
       <c r="B3" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137309281</v>
       </c>
       <c r="B4" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137309276</v>
       </c>
       <c r="B5" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137309280</v>
       </c>
       <c r="B6" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137309302</v>
       </c>
       <c r="B7" t="n">
-        <v>96896</v>
+        <v>96908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137309307</v>
       </c>
       <c r="B8" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>137309253</v>
       </c>
       <c r="B21" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>137309254</v>
       </c>
       <c r="B22" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>137309256</v>
       </c>
       <c r="B23" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>137309257</v>
       </c>
       <c r="B24" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>137309258</v>
       </c>
       <c r="B25" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>137309259</v>
       </c>
       <c r="B26" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>137309265</v>
       </c>
       <c r="B27" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>137309267</v>
       </c>
       <c r="B28" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>137309269</v>
       </c>
       <c r="B29" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>137309278</v>
       </c>
       <c r="B30" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>137309283</v>
       </c>
       <c r="B31" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>137309288</v>
       </c>
       <c r="B32" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>137309293</v>
       </c>
       <c r="B33" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>137309296</v>
       </c>
       <c r="B34" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>137309303</v>
       </c>
       <c r="B35" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 41767-2026 artfynd.xlsx
+++ b/artfynd/A 41767-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137309277</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137309279</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137309281</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137309276</v>
       </c>
       <c r="B5" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137309280</v>
       </c>
       <c r="B6" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137309302</v>
       </c>
       <c r="B7" t="n">
-        <v>96908</v>
+        <v>96909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137309307</v>
       </c>
       <c r="B8" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>137309253</v>
       </c>
       <c r="B21" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>137309254</v>
       </c>
       <c r="B22" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>137309256</v>
       </c>
       <c r="B23" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>137309257</v>
       </c>
       <c r="B24" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>137309258</v>
       </c>
       <c r="B25" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>137309259</v>
       </c>
       <c r="B26" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>137309265</v>
       </c>
       <c r="B27" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>137309267</v>
       </c>
       <c r="B28" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>137309269</v>
       </c>
       <c r="B29" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>137309278</v>
       </c>
       <c r="B30" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>137309283</v>
       </c>
       <c r="B31" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>137309288</v>
       </c>
       <c r="B32" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>137309293</v>
       </c>
       <c r="B33" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>137309296</v>
       </c>
       <c r="B34" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>137309303</v>
       </c>
       <c r="B35" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 41767-2026 artfynd.xlsx
+++ b/artfynd/A 41767-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137309277</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137309279</v>
       </c>
       <c r="B3" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137309281</v>
       </c>
       <c r="B4" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137309276</v>
       </c>
       <c r="B5" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137309280</v>
       </c>
       <c r="B6" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137309302</v>
       </c>
       <c r="B7" t="n">
-        <v>96909</v>
+        <v>96912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137309307</v>
       </c>
       <c r="B8" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>137309253</v>
       </c>
       <c r="B21" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>137309254</v>
       </c>
       <c r="B22" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>137309256</v>
       </c>
       <c r="B23" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>137309257</v>
       </c>
       <c r="B24" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>137309258</v>
       </c>
       <c r="B25" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>137309259</v>
       </c>
       <c r="B26" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>137309265</v>
       </c>
       <c r="B27" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>137309267</v>
       </c>
       <c r="B28" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>137309269</v>
       </c>
       <c r="B29" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>137309278</v>
       </c>
       <c r="B30" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>137309283</v>
       </c>
       <c r="B31" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>137309288</v>
       </c>
       <c r="B32" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>137309293</v>
       </c>
       <c r="B33" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>137309296</v>
       </c>
       <c r="B34" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>137309303</v>
       </c>
       <c r="B35" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 41767-2026 artfynd.xlsx
+++ b/artfynd/A 41767-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137309277</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137309279</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137309281</v>
       </c>
       <c r="B4" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137309276</v>
       </c>
       <c r="B5" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137309280</v>
       </c>
       <c r="B6" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137309302</v>
       </c>
       <c r="B7" t="n">
-        <v>96912</v>
+        <v>96916</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137309307</v>
       </c>
       <c r="B8" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137309262</v>
       </c>
       <c r="B9" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137309284</v>
       </c>
       <c r="B10" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>137309253</v>
       </c>
       <c r="B21" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>137309254</v>
       </c>
       <c r="B22" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>137309256</v>
       </c>
       <c r="B23" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>137309257</v>
       </c>
       <c r="B24" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>137309258</v>
       </c>
       <c r="B25" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>137309259</v>
       </c>
       <c r="B26" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>137309265</v>
       </c>
       <c r="B27" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>137309267</v>
       </c>
       <c r="B28" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>137309269</v>
       </c>
       <c r="B29" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>137309278</v>
       </c>
       <c r="B30" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>137309283</v>
       </c>
       <c r="B31" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>137309288</v>
       </c>
       <c r="B32" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>137309293</v>
       </c>
       <c r="B33" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>137309296</v>
       </c>
       <c r="B34" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>137309303</v>
       </c>
       <c r="B35" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
